--- a/NTu/Kipsigis_Tea_results.xlsx
+++ b/NTu/Kipsigis_Tea_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>99.72058677912322</v>
+        <v>104.2680344117504</v>
       </c>
       <c r="C3" t="n">
         <v>113.649862435789</v>
       </c>
       <c r="D3" t="n">
-        <v>13.92927565666581</v>
+        <v>9.38182802403864</v>
       </c>
       <c r="E3" t="n">
-        <v>13.92940991884031</v>
+        <v>9.381962286213138</v>
       </c>
       <c r="F3" t="n">
-        <v>51.0745030357478</v>
+        <v>34.40052838278151</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>92.40748414914187</v>
+        <v>99.35268884662982</v>
       </c>
       <c r="C4" t="n">
         <v>113.6498616437091</v>
       </c>
       <c r="D4" t="n">
-        <v>21.24237749456722</v>
+        <v>14.29717279707927</v>
       </c>
       <c r="E4" t="n">
-        <v>7.313101837901414</v>
+        <v>4.91534477304063</v>
       </c>
       <c r="F4" t="n">
-        <v>26.81470673897185</v>
+        <v>18.02293083448231</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>87.8251651402677</v>
+        <v>96.28865879121321</v>
       </c>
       <c r="C5" t="n">
         <v>113.6498609222855</v>
       </c>
       <c r="D5" t="n">
-        <v>25.8246957820178</v>
+        <v>17.36120213107229</v>
       </c>
       <c r="E5" t="n">
-        <v>4.582318287450576</v>
+        <v>3.06402933399302</v>
       </c>
       <c r="F5" t="n">
-        <v>16.80183372065211</v>
+        <v>11.23477422464107</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>84.70632608845399</v>
+        <v>94.22232448282428</v>
       </c>
       <c r="C6" t="n">
         <v>113.6498602652155</v>
       </c>
       <c r="D6" t="n">
-        <v>28.94353417676146</v>
+        <v>19.42753578239117</v>
       </c>
       <c r="E6" t="n">
-        <v>3.118838394743662</v>
+        <v>2.066333651318885</v>
       </c>
       <c r="F6" t="n">
-        <v>11.43574078072676</v>
+        <v>7.57655672150258</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>82.39429607867105</v>
+        <v>92.71042330466445</v>
       </c>
       <c r="C7" t="n">
         <v>113.6498596667584</v>
       </c>
       <c r="D7" t="n">
-        <v>31.25556358808737</v>
+        <v>20.93943636209397</v>
       </c>
       <c r="E7" t="n">
-        <v>2.312029411325909</v>
+        <v>1.511900579702797</v>
       </c>
       <c r="F7" t="n">
-        <v>8.477441174861667</v>
+        <v>5.543635458910255</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>80.54451694236579</v>
+        <v>91.51958821952131</v>
       </c>
       <c r="C8" t="n">
         <v>113.6498591216859</v>
       </c>
       <c r="D8" t="n">
-        <v>33.1053421793201</v>
+        <v>22.13027090216458</v>
       </c>
       <c r="E8" t="n">
-        <v>1.849778591232734</v>
+        <v>1.190834540070611</v>
       </c>
       <c r="F8" t="n">
-        <v>6.782521501186693</v>
+        <v>4.366393313592241</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>78.97421964472716</v>
+        <v>90.52538350031043</v>
       </c>
       <c r="C9" t="n">
         <v>113.6498586252358</v>
       </c>
       <c r="D9" t="n">
-        <v>34.67563898050865</v>
+        <v>23.12447512492538</v>
       </c>
       <c r="E9" t="n">
-        <v>1.570296801188547</v>
+        <v>0.9942042227607999</v>
       </c>
       <c r="F9" t="n">
-        <v>5.757754937691341</v>
+        <v>3.645415483456266</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>77.58522817647972</v>
+        <v>89.66042651810132</v>
       </c>
       <c r="C10" t="n">
         <v>113.6498581730708</v>
       </c>
       <c r="D10" t="n">
-        <v>36.06462999659111</v>
+        <v>23.98943165496951</v>
       </c>
       <c r="E10" t="n">
-        <v>1.388991016082457</v>
+        <v>0.8649565300441253</v>
       </c>
       <c r="F10" t="n">
-        <v>5.092967058969009</v>
+        <v>3.171507276828459</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>76.32385519832296</v>
+        <v>88.88741374227101</v>
       </c>
       <c r="C11" t="n">
         <v>113.6498577612406</v>
       </c>
       <c r="D11" t="n">
-        <v>37.32600256291764</v>
+        <v>24.76244401896959</v>
       </c>
       <c r="E11" t="n">
-        <v>1.261372566326528</v>
+        <v>0.7730123640000812</v>
       </c>
       <c r="F11" t="n">
-        <v>4.625032743197271</v>
+        <v>2.834378668000298</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>75.1599256167103</v>
+        <v>88.18499698937207</v>
       </c>
       <c r="C12" t="n">
         <v>113.6498573861471</v>
       </c>
       <c r="D12" t="n">
-        <v>38.48993176943682</v>
+        <v>25.46486039677505</v>
       </c>
       <c r="E12" t="n">
-        <v>1.163929206519185</v>
+        <v>0.7024163778054628</v>
       </c>
       <c r="F12" t="n">
-        <v>4.267740423903679</v>
+        <v>2.575526718620031</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>74.07575994084151</v>
+        <v>87.54035575102655</v>
       </c>
       <c r="C13" t="n">
         <v>113.6498570445133</v>
       </c>
       <c r="D13" t="n">
-        <v>39.57409710367176</v>
+        <v>26.10950129348672</v>
       </c>
       <c r="E13" t="n">
-        <v>1.084165334234939</v>
+        <v>0.6446408967116639</v>
       </c>
       <c r="F13" t="n">
-        <v>3.975272892194776</v>
+        <v>2.363683287942768</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>73.06037252854384</v>
+        <v>86.94527862569167</v>
       </c>
       <c r="C14" t="n">
         <v>113.6498567333544</v>
       </c>
       <c r="D14" t="n">
-        <v>40.58948420481052</v>
+        <v>26.70457810766268</v>
       </c>
       <c r="E14" t="n">
-        <v>1.015387101138757</v>
+        <v>0.5950768141759681</v>
       </c>
       <c r="F14" t="n">
-        <v>3.723086037508774</v>
+        <v>2.181948318645217</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>72.10640916287953</v>
+        <v>86.39408986191889</v>
       </c>
       <c r="C15" t="n">
         <v>113.649856449952</v>
       </c>
       <c r="D15" t="n">
-        <v>41.54344728707242</v>
+        <v>27.25576658803307</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9539630822619074</v>
+        <v>0.551188480370385</v>
       </c>
       <c r="F15" t="n">
-        <v>3.497864634960327</v>
+        <v>2.021024428024745</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>71.20852640989077</v>
+        <v>85.88254811720635</v>
       </c>
       <c r="C16" t="n">
         <v>113.64985619183</v>
       </c>
       <c r="D16" t="n">
-        <v>42.44132978193927</v>
+        <v>27.76730807462368</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8978824948668489</v>
+        <v>0.511541486590616</v>
       </c>
       <c r="F16" t="n">
-        <v>3.292235814511779</v>
+        <v>1.875652117498926</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>70.36253084562739</v>
+        <v>85.40725828901495</v>
       </c>
       <c r="C17" t="n">
         <v>113.6498559567335</v>
       </c>
       <c r="D17" t="n">
-        <v>43.28732511110609</v>
+        <v>28.24259766771853</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8459953291668114</v>
+        <v>0.4752895930948426</v>
       </c>
       <c r="F17" t="n">
-        <v>3.101982873611642</v>
+        <v>1.742728508014423</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>69.56491921884403</v>
+        <v>84.96535451867034</v>
       </c>
       <c r="C18" t="n">
         <v>113.6498557426084</v>
       </c>
       <c r="D18" t="n">
-        <v>44.08493652376437</v>
+        <v>28.68450122393806</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7976114126582843</v>
+        <v>0.441903556219529</v>
       </c>
       <c r="F18" t="n">
-        <v>2.924575179747043</v>
+        <v>1.620313039471607</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>68.81263043304673</v>
+        <v>84.55432679032587</v>
       </c>
       <c r="C19" t="n">
         <v>113.6498555475841</v>
       </c>
       <c r="D19" t="n">
-        <v>44.83722511453733</v>
+        <v>29.09552875725819</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7522885907729631</v>
+        <v>0.4110275333201372</v>
       </c>
       <c r="F19" t="n">
-        <v>2.758391499500865</v>
+        <v>1.50710095550717</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>68.10290963514936</v>
+        <v>84.17192378606573</v>
       </c>
       <c r="C20" t="n">
         <v>113.6498553699566</v>
       </c>
       <c r="D20" t="n">
-        <v>45.54694573480727</v>
+        <v>29.47793158389089</v>
       </c>
       <c r="E20" t="n">
-        <v>0.709720620269934</v>
+        <v>0.3824028266326991</v>
       </c>
       <c r="F20" t="n">
-        <v>2.602308940989758</v>
+        <v>1.40214369765323</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>67.43323180382961</v>
+        <v>83.81609642534146</v>
       </c>
       <c r="C21" t="n">
         <v>113.6498552081742</v>
       </c>
       <c r="D21" t="n">
-        <v>46.21662340434462</v>
+        <v>29.83375878283277</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6696776695373501</v>
+        <v>0.3558271989418813</v>
       </c>
       <c r="F21" t="n">
-        <v>2.455484788303617</v>
+        <v>1.304699729453565</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>66.80125706348153</v>
+        <v>83.48496327866097</v>
       </c>
       <c r="C22" t="n">
         <v>113.6498550608233</v>
       </c>
       <c r="D22" t="n">
-        <v>46.8485979973418</v>
+        <v>30.16489178216236</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6319745929971816</v>
+        <v>0.3311329993295828</v>
       </c>
       <c r="F22" t="n">
-        <v>2.317240174322999</v>
+        <v>1.214154330875137</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>66.20480304613312</v>
+        <v>83.1767878936718</v>
       </c>
       <c r="C23" t="n">
         <v>113.6498549266166</v>
       </c>
       <c r="D23" t="n">
-        <v>47.44505188048348</v>
+        <v>30.4730670329448</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5964538831416775</v>
+        <v>0.3081752507824405</v>
       </c>
       <c r="F23" t="n">
-        <v>2.186997571519484</v>
+        <v>1.129975919535615</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>65.6418265332063</v>
+        <v>82.88996274478315</v>
       </c>
       <c r="C24" t="n">
         <v>113.6498548043817</v>
       </c>
       <c r="D24" t="n">
-        <v>48.00802827117538</v>
+        <v>30.75989205959853</v>
       </c>
       <c r="E24" t="n">
-        <v>0.562976390691901</v>
+        <v>0.2868250266537302</v>
       </c>
       <c r="F24" t="n">
-        <v>2.064246765870303</v>
+        <v>1.051691764397011</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>65.11041025592584</v>
+        <v>82.62299698689444</v>
       </c>
       <c r="C25" t="n">
         <v>113.6498546930506</v>
       </c>
       <c r="D25" t="n">
-        <v>48.53944443712471</v>
+        <v>31.02685770615612</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5314161659493379</v>
+        <v>0.266965646557594</v>
       </c>
       <c r="F25" t="n">
-        <v>1.948525941814239</v>
+        <v>0.9788740373778447</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>64.6087526591987</v>
+        <v>82.37450649989565</v>
       </c>
       <c r="C26" t="n">
         <v>113.6498545916505</v>
       </c>
       <c r="D26" t="n">
-        <v>49.04110193245182</v>
+        <v>31.27534809175488</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5016574953271089</v>
+        <v>0.2484903855987568</v>
       </c>
       <c r="F26" t="n">
-        <v>1.839410816199399</v>
+        <v>0.9111314138621083</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>64.13515945183116</v>
+        <v>82.14320540237354</v>
       </c>
       <c r="C27" t="n">
         <v>113.6498544992957</v>
       </c>
       <c r="D27" t="n">
-        <v>49.51469504746457</v>
+        <v>31.50664909692219</v>
       </c>
       <c r="E27" t="n">
-        <v>0.473593115012747</v>
+        <v>0.2313010051673103</v>
       </c>
       <c r="F27" t="n">
-        <v>1.736508088380073</v>
+        <v>0.8481036856134713</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>63.68803630480798</v>
+        <v>81.92789858018612</v>
       </c>
       <c r="C28" t="n">
         <v>113.6498544151793</v>
       </c>
       <c r="D28" t="n">
-        <v>49.96181811037133</v>
+        <v>31.72195583499318</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4471230629067549</v>
+        <v>0.2153067380709928</v>
       </c>
       <c r="F28" t="n">
-        <v>1.639451230658101</v>
+        <v>0.7894580395936401</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>63.26588234521687</v>
+        <v>81.72747497125191</v>
       </c>
       <c r="C29" t="n">
         <v>113.6498543385664</v>
       </c>
       <c r="D29" t="n">
-        <v>50.38397199334951</v>
+        <v>31.92237936731448</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4221538829781863</v>
+        <v>0.2004235323212953</v>
       </c>
       <c r="F29" t="n">
-        <v>1.547897570920017</v>
+        <v>0.7348862851780827</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>62.86728424561377</v>
+        <v>81.54090145283777</v>
       </c>
       <c r="C30" t="n">
         <v>113.6498542687876</v>
       </c>
       <c r="D30" t="n">
-        <v>50.7825700231738</v>
+        <v>32.10895281594979</v>
       </c>
       <c r="E30" t="n">
-        <v>0.398598029824285</v>
+        <v>0.1865734486353148</v>
       </c>
       <c r="F30" t="n">
-        <v>1.461526109355712</v>
+        <v>0.6841026449961541</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>62.4909107901756</v>
+        <v>81.36721723449149</v>
       </c>
       <c r="C31" t="n">
         <v>113.6498542052333</v>
       </c>
       <c r="D31" t="n">
-        <v>51.15894341505771</v>
+        <v>32.28263697074182</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3763733918839094</v>
+        <v>0.1736841547920278</v>
       </c>
       <c r="F31" t="n">
-        <v>1.380035770241001</v>
+        <v>0.636841900904102</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>62.13550784312796</v>
+        <v>81.20552869110354</v>
       </c>
       <c r="C32" t="n">
         <v>113.6498541473483</v>
       </c>
       <c r="D32" t="n">
-        <v>51.51434630422037</v>
+        <v>32.4443254562448</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3554028891626686</v>
+        <v>0.1616884855029781</v>
       </c>
       <c r="F32" t="n">
-        <v>1.303143926929785</v>
+        <v>0.5928577801775864</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>61.79989366922458</v>
+        <v>81.0550045883235</v>
       </c>
       <c r="C33" t="n">
         <v>113.6498540946269</v>
       </c>
       <c r="D33" t="n">
-        <v>51.84996042540228</v>
+        <v>32.59484950630336</v>
       </c>
       <c r="E33" t="n">
-        <v>0.335614121181905</v>
+        <v>0.1505240500585643</v>
       </c>
       <c r="F33" t="n">
-        <v>1.230585111000319</v>
+        <v>0.5519215168814023</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>61.48295456977462</v>
+        <v>80.91487166300162</v>
       </c>
       <c r="C34" t="n">
         <v>113.6498540466084</v>
       </c>
       <c r="D34" t="n">
-        <v>52.16689947683376</v>
+        <v>32.73498238360676</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3169390514314827</v>
+        <v>0.140132877303401</v>
       </c>
       <c r="F34" t="n">
-        <v>1.16210985524877</v>
+        <v>0.5138205501124702</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>61.18364080576627</v>
+        <v>80.78441052782439</v>
       </c>
       <c r="C35" t="n">
         <v>113.6498540028733</v>
       </c>
       <c r="D35" t="n">
-        <v>52.46621319710702</v>
+        <v>32.86544347504889</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2993137202732541</v>
+        <v>0.1304610914421289</v>
       </c>
       <c r="F35" t="n">
-        <v>1.097483641001932</v>
+        <v>0.4783573352878061</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>60.90096278462432</v>
+        <v>80.66295187363785</v>
       </c>
       <c r="C36" t="n">
         <v>113.6498539630395</v>
       </c>
       <c r="D36" t="n">
-        <v>52.74889117841519</v>
+        <v>32.98690208940165</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2826779813081686</v>
+        <v>0.1214586143527612</v>
       </c>
       <c r="F36" t="n">
-        <v>1.036485931463285</v>
+        <v>0.445348252626791</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>60.63398749044098</v>
+        <v>80.54987294605026</v>
       </c>
       <c r="C37" t="n">
         <v>113.6498539267591</v>
       </c>
       <c r="D37" t="n">
-        <v>53.01586643631807</v>
+        <v>33.09998098070879</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2669752579028852</v>
+        <v>0.1130788913071399</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9789092789772459</v>
+        <v>0.4146226014595129</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>60.38183513987144</v>
+        <v>80.44459427528329</v>
       </c>
       <c r="C38" t="n">
         <v>113.6498538937149</v>
       </c>
       <c r="D38" t="n">
-        <v>53.26801875384349</v>
+        <v>33.20525961843164</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2521523175254217</v>
+        <v>0.1052786377228472</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9245584975932127</v>
+        <v>0.3860216716504397</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>60.1436760476825</v>
+        <v>80.34657664017853</v>
       </c>
       <c r="C39" t="n">
         <v>113.6498538636185</v>
       </c>
       <c r="D39" t="n">
-        <v>53.50617781593605</v>
+        <v>33.30327722344002</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2381590620925564</v>
+        <v>0.09801760500837986</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8732498943393736</v>
+        <v>0.3593978850307262</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>59.91872768739507</v>
+        <v>80.25531824890614</v>
       </c>
       <c r="C40" t="n">
         <v>113.6498538362068</v>
       </c>
       <c r="D40" t="n">
-        <v>53.73112614881172</v>
+        <v>33.39453558730065</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2249483328756696</v>
+        <v>0.09125836386063213</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8248105538774553</v>
+        <v>0.3346140008223178</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>59.7062519336913</v>
+        <v>80.17035212036075</v>
       </c>
       <c r="C41" t="n">
         <v>113.6498538112403</v>
       </c>
       <c r="D41" t="n">
-        <v>53.94360187754902</v>
+        <v>33.47950169087957</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2124757287373029</v>
+        <v>0.08496610357892109</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7790776720367774</v>
+        <v>0.3115423797893773</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>59.50555247432695</v>
+        <v>80.09124365150834</v>
       </c>
       <c r="C42" t="n">
         <v>113.6498537885009</v>
       </c>
       <c r="D42" t="n">
-        <v>54.14430131417397</v>
+        <v>33.55861013699258</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2006994366249444</v>
+        <v>0.07910844611301115</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7358979342914628</v>
+        <v>0.2900643024143743</v>
       </c>
     </row>
   </sheetData>
